--- a/spreadsheets/domains/cramps-clim_CRAMPS-CLIM_Workbook.xlsx
+++ b/spreadsheets/domains/cramps-clim_CRAMPS-CLIM_Workbook.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="Rc4de218d2ae94d82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="R527f11d5218745e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="Rf5f25ebf2e1d4cde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="R70a02de7cde74197"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gotchas" sheetId="5" r:id="R128e23bc713f48dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="Rf13a4747488a4eeb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="Rb2748e678e58449a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="R62e51ae5b16f416b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Checkpoints" sheetId="9" r:id="R093c442bb75d488b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reliance Positioning" sheetId="10" r:id="R6ff9045a8a754156"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="R2e682765944f4729"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="R1677e3f4f5064ade"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="R4802eeba485843a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="Re8fbc1925cbc4afb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failure Modes" sheetId="5" r:id="Rd2952f9360c248ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="R92ecab7b77c94583"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="Re64560fe57154816"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="Rb8268c8c16d2496f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Checkpoints" sheetId="9" r:id="Re82de1fdf11e4a69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reliance Positioning" sheetId="10" r:id="R32c2dc814c5d4b76"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -250,7 +250,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>Gotchas</x:v>
+        <x:v>Primary failure modes</x:v>
       </x:c>
       <x:c r="B7" t="str">
         <x:v>spatial autocorrelation; temporal autocorrelation; non-stationary baseline; model-family dependence</x:v>
@@ -1089,7 +1089,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
-        <x:v>Gotcha</x:v>
+        <x:v>Failure mode</x:v>
       </x:c>
       <x:c r="B1" t="str">
         <x:v>Status</x:v>
@@ -1255,7 +1255,7 @@
       <x:c r="B6" t="str"/>
       <x:c r="C6" t="str"/>
       <x:c r="D6" t="str">
-        <x:v>raw rows, source trace, extraction confidence, review status, quarantine log</x:v>
+        <x:v>raw signal rows, source trace, extraction confidence, review status, quarantine log</x:v>
       </x:c>
       <x:c r="E6" t="str"/>
     </x:row>
